--- a/Catch and index models/JABBA_macarellus/jabba_posteriores_conjuntas.xlsx
+++ b/Catch and index models/JABBA_macarellus/jabba_posteriores_conjuntas.xlsx
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1626.49348240219</v>
+        <v>1606.619937226657</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -484,7 +484,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>2512.117556342088</v>
+        <v>2313.201948186716</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>3352.543086134689</v>
+        <v>3018.952066832316</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4837.353503210515</v>
+        <v>4325.087990088022</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -508,7 +508,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>11494.30094963454</v>
+        <v>10573.75098139131</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.02460618753767205</v>
+        <v>0.02162556105738398</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -542,7 +542,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.8902002942391136</v>
+        <v>0.8693109501554954</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -550,7 +550,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.9529449513807027</v>
+        <v>0.9466892850738285</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -558,7 +558,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.000453832460478</v>
+        <v>0.9960782618499993</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -566,7 +566,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1.103676092461631</v>
+        <v>1.094937483025667</v>
       </c>
     </row>
   </sheetData>
@@ -607,13 +607,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>2.42919551658551E-05</v>
+        <v>3.539316686452677E-05</v>
       </c>
       <c r="D2">
-        <v>5.505192780048972E-06</v>
+        <v>5.856441657297401E-06</v>
       </c>
       <c r="E2">
-        <v>0.0001299293500843792</v>
+        <v>0.0001458043566206796</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -624,13 +624,13 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>6.538973257892581E-05</v>
+        <v>7.16835025974059E-05</v>
       </c>
       <c r="D3">
-        <v>1.473290826448176E-05</v>
+        <v>1.294269647224053E-05</v>
       </c>
       <c r="E3">
-        <v>0.0001459916803044589</v>
+        <v>0.0001773575825874234</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -641,16 +641,16 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>0.0002561723337358833</v>
+        <v>0.0002373626576560093</v>
       </c>
       <c r="D4">
-        <v>1.339753314352618E-05</v>
+        <v>1.18578668497231E-05</v>
       </c>
       <c r="E4">
-        <v>0.001625484859482849</v>
+        <v>0.002268014138983722</v>
       </c>
       <c r="F4">
-        <v>3.292036585226835</v>
+        <v>3.191567453584709</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -661,13 +661,13 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>3.830777115982299E-05</v>
+        <v>4.012473530815473E-05</v>
       </c>
       <c r="D5">
-        <v>1.3895874450618E-05</v>
+        <v>1.277184942887267E-05</v>
       </c>
       <c r="E5">
-        <v>9.522563158163319E-05</v>
+        <v>0.0001079062294460208</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -678,16 +678,16 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>3.448266840747581E-05</v>
+        <v>3.389208357985391E-05</v>
       </c>
       <c r="D6">
-        <v>1.241502366408545E-05</v>
+        <v>1.089323591325117E-05</v>
       </c>
       <c r="E6">
-        <v>8.921113283483715E-05</v>
+        <v>9.124278171581321E-05</v>
       </c>
       <c r="F6">
-        <v>0.8981765320087693</v>
+        <v>0.8488285496439456</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -698,13 +698,13 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>2.929752774011285E-05</v>
+        <v>0.0001623874764242056</v>
       </c>
       <c r="D7">
-        <v>7.812880454738811E-06</v>
+        <v>9.327231998007645E-06</v>
       </c>
       <c r="E7">
-        <v>8.052559713271668E-05</v>
+        <v>0.001432628816479786</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -715,13 +715,13 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>4.51658596460881E-05</v>
+        <v>4.798888029989698E-05</v>
       </c>
       <c r="D8">
-        <v>1.218377786315416E-05</v>
+        <v>1.408545052405846E-05</v>
       </c>
       <c r="E8">
-        <v>0.0001333576870460881</v>
+        <v>0.0001244052671854677</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -732,16 +732,16 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>4.031264013516754E-05</v>
+        <v>4.043802363499405E-05</v>
       </c>
       <c r="D9">
-        <v>1.154190931548224E-05</v>
+        <v>1.253463754449556E-05</v>
       </c>
       <c r="E9">
-        <v>0.000111158491038059</v>
+        <v>0.0001025723621118917</v>
       </c>
       <c r="F9">
-        <v>0.8860596259287727</v>
+        <v>0.8482523099806329</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -752,13 +752,13 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>2.719823399103564E-05</v>
+        <v>3.00499409648815E-05</v>
       </c>
       <c r="D10">
-        <v>9.732544068712249E-06</v>
+        <v>9.983364200855354E-06</v>
       </c>
       <c r="E10">
-        <v>6.817077632221725E-05</v>
+        <v>7.575318850902262E-05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -769,16 +769,16 @@
         <v>17</v>
       </c>
       <c r="C11">
-        <v>2.536514809739749E-05</v>
+        <v>2.566337576323996E-05</v>
       </c>
       <c r="D11">
-        <v>8.879391473900633E-06</v>
+        <v>8.506516941233583E-06</v>
       </c>
       <c r="E11">
-        <v>6.581672623569816E-05</v>
+        <v>6.858656429601986E-05</v>
       </c>
       <c r="F11">
-        <v>0.9385414254306628</v>
+        <v>0.8532353609029493</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -789,13 +789,13 @@
         <v>16</v>
       </c>
       <c r="C12">
-        <v>5.562585843478957E-05</v>
+        <v>5.987676113526382E-05</v>
       </c>
       <c r="D12">
-        <v>1.622919157754693E-05</v>
+        <v>1.947585229599026E-05</v>
       </c>
       <c r="E12">
-        <v>0.0001490246675432702</v>
+        <v>0.000142705305989595</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -806,16 +806,16 @@
         <v>17</v>
       </c>
       <c r="C13">
-        <v>4.908991119554344E-05</v>
+        <v>5.077836126425809E-05</v>
       </c>
       <c r="D13">
-        <v>1.54353268700667E-05</v>
+        <v>1.708202990055399E-05</v>
       </c>
       <c r="E13">
-        <v>0.0001235857373826199</v>
+        <v>0.0001217471858921484</v>
       </c>
       <c r="F13">
-        <v>0.8826133103123468</v>
+        <v>0.8512913833982914</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -826,13 +826,13 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.952300322246316E-05</v>
+        <v>2.727652486281499E-05</v>
       </c>
       <c r="D14">
-        <v>7.342338641940313E-06</v>
+        <v>6.340517674959908E-06</v>
       </c>
       <c r="E14">
-        <v>8.352177688567333E-05</v>
+        <v>7.377864681841878E-05</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -843,13 +843,13 @@
         <v>16</v>
       </c>
       <c r="C15">
-        <v>0.00011495299437326</v>
+        <v>9.888161052745054E-05</v>
       </c>
       <c r="D15">
-        <v>5.807926693659443E-05</v>
+        <v>5.142176881273878E-05</v>
       </c>
       <c r="E15">
-        <v>0.0001979336139033285</v>
+        <v>0.0001785084705764567</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -860,16 +860,16 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>0.0002914253353772456</v>
+        <v>7.739628453915513E-05</v>
       </c>
       <c r="D16">
-        <v>4.455409569469997E-05</v>
+        <v>3.853967200052407E-05</v>
       </c>
       <c r="E16">
-        <v>0.002262980899119333</v>
+        <v>0.0001548656578068105</v>
       </c>
       <c r="F16">
-        <v>2.461915050287418</v>
+        <v>0.7846137024757444</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -880,13 +880,13 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>1.561927102717508E-05</v>
+        <v>1.734853148114007E-05</v>
       </c>
       <c r="D17">
-        <v>6.08466697637157E-06</v>
+        <v>7.001516129382665E-06</v>
       </c>
       <c r="E17">
-        <v>3.889807536982939E-05</v>
+        <v>4.168883912667458E-05</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -897,16 +897,16 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>1.498719498421134E-05</v>
+        <v>1.550447006290756E-05</v>
       </c>
       <c r="D18">
-        <v>5.549307393514771E-06</v>
+        <v>6.033395172368091E-06</v>
       </c>
       <c r="E18">
-        <v>3.92237955476662E-05</v>
+        <v>4.133983345006079E-05</v>
       </c>
       <c r="F18">
-        <v>0.9573693167279359</v>
+        <v>0.8988244876495868</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -917,13 +917,13 @@
         <v>9</v>
       </c>
       <c r="C19">
-        <v>3.145961410369385E-05</v>
+        <v>3.847027331797679E-05</v>
       </c>
       <c r="D19">
-        <v>8.781449692202751E-06</v>
+        <v>1.320078225102023E-05</v>
       </c>
       <c r="E19">
-        <v>8.574718215290117E-05</v>
+        <v>0.0001041654289408794</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="C20">
-        <v>3.753200272017663E-05</v>
+        <v>7.688916410480641E-05</v>
       </c>
       <c r="D20">
-        <v>1.206517907720004E-05</v>
+        <v>1.598300880681596E-05</v>
       </c>
       <c r="E20">
-        <v>9.315615983476795E-05</v>
+        <v>0.0001624255800867561</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -951,16 +951,16 @@
         <v>17</v>
       </c>
       <c r="C21">
-        <v>3.296312542590124E-05</v>
+        <v>0.0002563964270461529</v>
       </c>
       <c r="D21">
-        <v>1.058704913787228E-05</v>
+        <v>1.347166054284686E-05</v>
       </c>
       <c r="E21">
-        <v>8.645378513967947E-05</v>
+        <v>0.001741275534769463</v>
       </c>
       <c r="F21">
-        <v>0.8917115422364947</v>
+        <v>3.536546561986575</v>
       </c>
     </row>
     <row r="22" spans="1:6">
